--- a/output/Data and Chart Outputs/el_salvador_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/el_salvador_power_generation_daily.xlsx
@@ -379,6 +379,18 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="3"/>

--- a/output/Data and Chart Outputs/el_salvador_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/el_salvador_power_generation_daily.xlsx
@@ -21,8 +21,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,12 +62,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -797,7 +798,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -819,7 +819,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -841,7 +840,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
@@ -916,7 +914,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B2" t="n">
@@ -942,7 +940,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B3" t="n">
@@ -968,7 +966,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B4" t="n">
@@ -994,7 +992,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B5" t="n">
@@ -1020,7 +1018,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B6" t="n">
@@ -1046,7 +1044,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B7" t="n">
@@ -1072,7 +1070,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B8" t="n">
@@ -1098,7 +1096,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B9" t="n">
@@ -1124,7 +1122,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B10" t="n">
@@ -1150,7 +1148,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B11" t="n">
@@ -1176,7 +1174,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B12" t="n">
@@ -1202,7 +1200,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B13" t="n">
@@ -1228,7 +1226,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B14" t="n">
@@ -1254,7 +1252,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B15" t="n">
@@ -1280,7 +1278,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B16" t="n">
@@ -1306,7 +1304,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B17" t="n">
@@ -1332,7 +1330,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B18" t="n">
@@ -1358,7 +1356,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B19" t="n">
@@ -1384,7 +1382,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B20" t="n">
@@ -1410,7 +1408,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B21" t="n">
@@ -1436,7 +1434,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B22" t="n">
@@ -1462,7 +1460,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B23" t="n">
@@ -1488,7 +1486,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B24" t="n">
@@ -1514,7 +1512,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B25" t="n">
@@ -1540,7 +1538,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B26" t="n">
@@ -1566,7 +1564,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B27" t="n">
@@ -1592,7 +1590,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B28" t="n">
@@ -1618,7 +1616,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B29" t="n">
@@ -1644,7 +1642,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B30" t="n">
@@ -1670,7 +1668,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B31" t="n">
@@ -1696,7 +1694,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B32" t="n">
@@ -1722,7 +1720,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B33" t="n">
@@ -1748,7 +1746,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B34" t="n">
@@ -1774,7 +1772,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B35" t="n">
@@ -1800,7 +1798,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B36" t="n">
@@ -1826,7 +1824,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B37" t="n">

--- a/output/Data and Chart Outputs/el_salvador_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/el_salvador_power_generation_daily.xlsx
@@ -157,6 +157,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>El Salvador power generation by type (SIGET, monthly net) (to Dec/25)</a:t>
             </a:r>
           </a:p>

--- a/output/Data and Chart Outputs/el_salvador_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/el_salvador_power_generation_daily.xlsx
@@ -21,8 +21,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,13 +62,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -799,6 +798,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -820,6 +820,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -841,6 +842,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
@@ -915,7 +917,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B2" t="n">
@@ -941,7 +943,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B3" t="n">
@@ -967,7 +969,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B4" t="n">
@@ -993,7 +995,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B5" t="n">
@@ -1019,7 +1021,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B6" t="n">
@@ -1045,7 +1047,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B7" t="n">
@@ -1071,7 +1073,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B8" t="n">
@@ -1097,7 +1099,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B9" t="n">
@@ -1123,7 +1125,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B10" t="n">
@@ -1149,7 +1151,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B11" t="n">
@@ -1175,7 +1177,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B12" t="n">
@@ -1201,7 +1203,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B13" t="n">
@@ -1227,7 +1229,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B14" t="n">
@@ -1253,7 +1255,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B15" t="n">
@@ -1279,7 +1281,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B16" t="n">
@@ -1305,7 +1307,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B17" t="n">
@@ -1331,7 +1333,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B18" t="n">
@@ -1357,7 +1359,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B19" t="n">
@@ -1383,7 +1385,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B20" t="n">
@@ -1409,7 +1411,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B21" t="n">
@@ -1435,7 +1437,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B22" t="n">
@@ -1461,7 +1463,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B23" t="n">
@@ -1487,7 +1489,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B24" t="n">
@@ -1513,7 +1515,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B25" t="n">
@@ -1539,7 +1541,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B26" t="n">
@@ -1565,7 +1567,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B27" t="n">
@@ -1591,7 +1593,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B28" t="n">
@@ -1617,7 +1619,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B29" t="n">
@@ -1643,7 +1645,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B30" t="n">
@@ -1669,7 +1671,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B31" t="n">
@@ -1695,7 +1697,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B32" t="n">
@@ -1721,7 +1723,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B33" t="n">
@@ -1747,7 +1749,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B34" t="n">
@@ -1773,7 +1775,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B35" t="n">
@@ -1799,7 +1801,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B36" t="n">
@@ -1825,7 +1827,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B37" t="n">
